--- a/AAII_Financials/Quarterly/CRBG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CRBG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="92">
   <si>
     <t>CRBG</t>
   </si>
@@ -656,314 +656,326 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="22" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="23" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>3995000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3757000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6580000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5183000</v>
       </c>
-      <c r="G8" s="3">
-        <v>3156000</v>
-      </c>
       <c r="H8" s="3">
+        <v>3174000</v>
+      </c>
+      <c r="I8" s="3">
         <v>3680000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>6224000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2935000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3618000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5789000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3579000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5390000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5870000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4244000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3905000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>6294000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>6540000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>6931000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>6551000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5231000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3392000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>7041000</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>3040000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2848000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5037000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>4472000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2895000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3305000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3467000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2908000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2729000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4416000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4491000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2650000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>4365000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3913000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>262000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>263000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>252000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>243000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>181000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>388000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>48000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>440000</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>955000</v>
+      </c>
+      <c r="E10" s="3">
         <v>909000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1543000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>711000</v>
       </c>
-      <c r="G10" s="3">
-        <v>261000</v>
-      </c>
       <c r="H10" s="3">
+        <v>279000</v>
+      </c>
+      <c r="I10" s="3">
         <v>375000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2757000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>27000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>889000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1373000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-912000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2740000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1505000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>331000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3643000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>6031000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>6288000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>6688000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>6370000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>4843000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3344000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>6601000</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -989,8 +1001,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1060,8 +1073,11 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1131,17 +1147,20 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>-2000</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1151,104 +1170,107 @@
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>1000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-241000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-5000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-621000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-59000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>3000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>22000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-2000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1000</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>-2988000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-103000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>214000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>15000</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>173000</v>
+      </c>
+      <c r="E15" s="3">
         <v>165000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>174000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>199000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>94000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>89000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>61000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>36000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>32000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>64000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>20000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>107000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>134000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>105000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1273,8 +1295,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1297,150 +1322,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3551000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3360000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5585000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5024000</v>
       </c>
-      <c r="G17" s="3">
-        <v>3458000</v>
-      </c>
       <c r="H17" s="3">
+        <v>3476000</v>
+      </c>
+      <c r="I17" s="3">
         <v>3901000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4016000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3456000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3294000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5056000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5121000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3326000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5033000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4560000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4280000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3408000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3132000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2783000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1834000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3195000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3713000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2957000</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>444000</v>
+      </c>
+      <c r="E18" s="3">
         <v>397000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>995000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>159000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-302000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-221000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2208000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-521000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>324000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>733000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1542000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2064000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>837000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-316000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-375000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2886000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3408000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>4148000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>4717000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2036000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-321000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>4084000</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1466,65 +1498,66 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>261000</v>
+      </c>
+      <c r="E20" s="3">
         <v>171000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-108000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>66000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>169000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>493000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-862000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>939000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-29000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-416000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>703000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-533000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-149000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>178000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>245000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>435000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>45000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>233000</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
@@ -1534,82 +1567,88 @@
       <c r="X20" s="3">
         <v>0</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>356000</v>
+      </c>
+      <c r="E21" s="3">
         <v>391000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1277000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>292000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-377000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-625000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3131000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1424000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>385000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1213000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-2225000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2704000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1120000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-389000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-7000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>3460000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3619000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>4538000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>4708000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2223000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-372000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>4519000</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1617,212 +1656,221 @@
         <v>131000</v>
       </c>
       <c r="E22" s="3">
+        <v>131000</v>
+      </c>
+      <c r="F22" s="3">
         <v>132000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>135000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>137000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>148000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>145000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>133000</v>
-      </c>
-      <c r="K22" s="3">
-        <v>138000</v>
       </c>
       <c r="L22" s="3">
         <v>138000</v>
       </c>
       <c r="M22" s="3">
+        <v>138000</v>
+      </c>
+      <c r="N22" s="3">
         <v>139000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>135000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>134000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>172000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>177000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>149000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>127000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>81000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>94000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>83000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>98000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>114000</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>52000</v>
+      </c>
+      <c r="E23" s="3">
         <v>97000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>971000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-42000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-608000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-862000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2925000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1594000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>456000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1016000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1763000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2461000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>911000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-669000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-307000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3172000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3326000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>4300000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>4623000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1953000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-419000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>3970000</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>50000</v>
+      </c>
+      <c r="E24" s="3">
         <v>158000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>173000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-179000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>60000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-205000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>703000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-407000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>115000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>189000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-432000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>392000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>160000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-216000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-139000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>640000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>652000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>859000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>884000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>381000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-181000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>759000</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1892,150 +1940,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-61000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>798000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>137000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-668000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-657000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2222000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1187000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>341000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>827000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1331000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2069000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>751000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-453000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-168000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2532000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2674000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>3441000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>3739000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1572000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-238000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>3211000</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-53000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>814000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>144000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-660000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-664000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2171000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1184000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>365000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>878000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1309000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2101000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>771000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-459000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-207000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2406000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2594000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>3366000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>3122000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1420000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-303000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>3116000</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2105,8 +2162,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2176,8 +2236,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2247,8 +2310,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2318,65 +2384,68 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-261000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-171000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>108000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-66000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-169000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-493000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>862000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-939000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>29000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>416000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-703000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>533000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>149000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-178000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-245000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-435000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-45000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-233000</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
@@ -2386,82 +2455,88 @@
       <c r="X32" s="3">
         <v>0</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-53000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>814000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>144000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-660000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-664000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2171000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1184000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>365000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>878000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1309000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2101000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>771000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-459000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-207000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2406000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2594000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>3366000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>3122000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1420000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-303000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>3116000</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2531,155 +2606,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-53000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>814000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>144000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-660000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-664000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2171000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1184000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>365000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>878000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1309000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2101000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>771000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-459000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-207000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2406000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2594000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>3366000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>3122000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1420000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-303000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>3116000</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2705,8 +2789,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2732,124 +2817,128 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>353000</v>
+      </c>
+      <c r="E41" s="3">
         <v>373000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>447000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>316000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>290000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>393000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>806000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>530000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>637000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>410000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>612000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>569000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>751000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>465000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>552000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>382000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>457000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>583000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>537000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>518000</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>4584000</v>
+      </c>
+      <c r="E42" s="3">
         <v>4725000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>5671000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>4639000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3807000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>6228000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>4977000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>4895000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>4995000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>4141000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>4333000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>4727000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>4038000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>3951000</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -2874,53 +2963,56 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>464000</v>
+      </c>
+      <c r="E43" s="3">
         <v>534000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>648000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>621000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>674000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>668000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>713000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>690000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>620000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>586000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>594000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>717000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>739000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>745000</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
@@ -2945,8 +3037,11 @@
       <c r="Y43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2989,8 +3084,8 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3016,53 +3111,56 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>28949000</v>
+      </c>
+      <c r="E45" s="3">
         <v>29013000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>28871000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>29418000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>29168000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>28879000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>28855000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>30859000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>29671000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>32642000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>33030000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>31394000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>31710000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>31804000</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -3087,53 +3185,56 @@
       <c r="Y45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>34353000</v>
+      </c>
+      <c r="E46" s="3">
         <v>34648000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>35641000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>34998000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>33943000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>36172000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>35355000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>36991000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>35939000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>37795000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>38572000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>37419000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>37275000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>37024000</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -3158,123 +3259,129 @@
       <c r="Y46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>205101000</v>
+      </c>
+      <c r="E47" s="3">
         <v>203543000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>204117000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>201613000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>194669000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>189218000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>184583000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>192198000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>180563000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>181688000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>179493000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>164267000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>169994000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>171983000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>220912000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>213806000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>223790000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>239783000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>256318000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>254682000</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F48" s="3">
         <v>79000</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I48" s="3">
+      <c r="I48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J48" s="3">
         <v>75000</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N48" s="3">
         <v>20000</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q48" s="3">
-        <v>0</v>
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R48" s="3">
         <v>0</v>
@@ -3300,53 +3407,56 @@
       <c r="Y48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8836000</v>
+      </c>
+      <c r="E49" s="3">
         <v>8785000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8885000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8808000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>10435000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>10328000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>10293000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>10204000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10133000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>10049000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>10011000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>9973000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>10715000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>10641000</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
-      </c>
       <c r="R49" s="3">
         <v>0</v>
       </c>
@@ -3371,8 +3481,11 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3442,8 +3555,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3513,79 +3629,85 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>106357000</v>
+      </c>
+      <c r="E52" s="3">
         <v>98274000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>102877000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>104510000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>98356000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>93358000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>98420000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>100750000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>98975000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>99879000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>95730000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>89094000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>94765000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>92739000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>8843000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>9715000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>7778000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6381000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4837000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4479000</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3655,79 +3777,85 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>415793000</v>
+      </c>
+      <c r="E54" s="3">
         <v>407060000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>413547000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>411294000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>399163000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>390022000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>389397000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>399422000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>382492000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>385588000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>379270000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>355592000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>367470000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>366691000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>360322000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>354595000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>368271000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>394667000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>416212000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>414231000</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3753,8 +3881,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3780,8 +3909,9 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3824,8 +3954,8 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R57" s="3">
         <v>0</v>
@@ -3851,46 +3981,49 @@
       <c r="Y57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4850000</v>
+      </c>
+      <c r="E58" s="3">
         <v>6200000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4518000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3700000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3101000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4701000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4101000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5000000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1850000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3850000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2750000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1000000</v>
-      </c>
-      <c r="O58" s="3">
-        <v>1500000</v>
       </c>
       <c r="P58" s="3">
         <v>1500000</v>
@@ -3902,17 +4035,17 @@
         <v>1500000</v>
       </c>
       <c r="S58" s="3">
+        <v>1500000</v>
+      </c>
+      <c r="T58" s="3">
         <v>1895000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>8346000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>8317000</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3922,124 +4055,130 @@
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>23243000</v>
+      </c>
+      <c r="E59" s="3">
         <v>23283000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>23947000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>24145000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>23948000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>24072000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>24401000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>26118000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>25124000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>27254000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>27844000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>26082000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>26164000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>29137000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>243796000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>242363000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>246535000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>260452000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>268806000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>264976000</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>28093000</v>
+      </c>
+      <c r="E60" s="3">
         <v>29483000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>28465000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>27845000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>27049000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>28773000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>28502000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>31118000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>26974000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>31104000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>30594000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>27082000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>27664000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>30637000</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -4064,124 +4203,130 @@
       <c r="Y60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>9620000</v>
+      </c>
+      <c r="E61" s="3">
         <v>10924000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>10968000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>11016000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>11248000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>11214000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>11371000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>12014000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>11485000</v>
-      </c>
-      <c r="L61" s="3">
-        <v>11648000</v>
       </c>
       <c r="M61" s="3">
         <v>11648000</v>
       </c>
       <c r="N61" s="3">
+        <v>11648000</v>
+      </c>
+      <c r="O61" s="3">
         <v>10967000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>10527000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>10559000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>13826000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>13863000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>13664000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>7313000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>7363000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>7762000</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>366707000</v>
+      </c>
+      <c r="E62" s="3">
         <v>355112000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>360154000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>358111000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>347697000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>337199000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>337198000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>341848000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>332221000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>330450000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>324393000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>308287000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>317811000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>313030000</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4191,8 +4336,8 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U62" s="3">
-        <v>0</v>
+      <c r="U62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V62" s="3">
         <v>0</v>
@@ -4206,8 +4351,11 @@
       <c r="Y62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4277,8 +4425,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4348,8 +4499,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4419,79 +4573,85 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>404420000</v>
+      </c>
+      <c r="E66" s="3">
         <v>395519000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>399587000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>396972000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>385994000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>377186000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>377071000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>384980000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>370680000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>373202000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>366635000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>346336000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>356002000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>354226000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>350942000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>347066000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>356388000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>375186000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>389126000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>377722000</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4517,8 +4677,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4588,8 +4749,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4659,8 +4823,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4671,7 +4838,7 @@
         <v>493000</v>
       </c>
       <c r="F70" s="3">
-        <v>0</v>
+        <v>493000</v>
       </c>
       <c r="G70" s="3">
         <v>0</v>
@@ -4730,8 +4897,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4801,79 +4971,85 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>18075000</v>
+      </c>
+      <c r="E72" s="3">
         <v>18204000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>18373000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>17677000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>17669000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>18461000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>19257000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>17218000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>18536000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>18310000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>17572000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>19765000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>17811000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>17592000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>18207000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>16783000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>14643000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>12030000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>8859000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>25913000</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4943,8 +5119,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5014,8 +5193,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5085,79 +5267,85 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10158000</v>
+      </c>
+      <c r="E76" s="3">
         <v>10312000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12708000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>13542000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12302000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11980000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>11462000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>13608000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>10996000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11576000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>11766000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8366000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10561000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>11555000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9380000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>7529000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>11883000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>19481000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>27086000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>36509000</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5227,155 +5415,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-53000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>814000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>144000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-660000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-664000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2171000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1184000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>365000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>878000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1309000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2101000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>771000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-459000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-207000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2406000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2594000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>3366000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>3122000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1420000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-303000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>3116000</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5401,79 +5598,83 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>94000</v>
+      </c>
+      <c r="E83" s="3">
         <v>89000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>61000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>36000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>32000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>64000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>20000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>107000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>134000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>105000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>123000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>139000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>166000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>157000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>-34000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>227000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>359000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>469000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>-9000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>187000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>-51000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>435000</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5543,8 +5744,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5614,8 +5818,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5685,8 +5892,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5756,8 +5966,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5827,79 +6040,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-44000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-9000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1881000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>24000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-259000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>375000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1479000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>83000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-9000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>598000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>767000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1018000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1271000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>301000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>493000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1633000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>554000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>15000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>865000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>167000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>856000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>573000</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5925,8 +6144,9 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5969,8 +6189,8 @@
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -5996,8 +6216,11 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6067,8 +6290,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6138,79 +6364,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1565000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2533000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3470000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3317000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2672000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3873000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1349000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-6223000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1319000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2645000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2209000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2377000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>587000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1477000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3923000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-875000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1209000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1246000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>1077000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1526000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1992000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>474000</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6236,64 +6468,65 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>112000</v>
+      </c>
+      <c r="E96" s="3">
         <v>114000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>119000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>128000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>131000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>133000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>129000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>133000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>139000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>143000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>876000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>146000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>551000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>149000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-296000</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
-        <v>-290000</v>
+        <v>0</v>
       </c>
       <c r="T96" s="3">
         <v>-290000</v>
       </c>
       <c r="U96" s="3">
-        <v>0</v>
+        <v>-290000</v>
       </c>
       <c r="V96" s="3">
         <v>0</v>
@@ -6307,8 +6540,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6378,8 +6614,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6449,8 +6688,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6520,217 +6762,229 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1541000</v>
+      </c>
+      <c r="E100" s="3">
         <v>2467000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1720000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>3317000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2828000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3074000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>146000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>6034000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1556000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1844000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1454000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1190000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1595000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1065000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>3642000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-820000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>602000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1250000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1906000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>930000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1094000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-927000</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1000</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G101" s="3">
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3">
         <v>-1000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1000</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
       <c r="J101" s="3">
         <v>0</v>
       </c>
       <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>1000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>2000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-5000</v>
-      </c>
-      <c r="O101" s="3">
-        <v>-2000</v>
       </c>
       <c r="P101" s="3">
         <v>-2000</v>
       </c>
       <c r="Q101" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="R101" s="3">
         <v>-1000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-5000</v>
-      </c>
-      <c r="S101" s="3">
-        <v>-2000</v>
       </c>
       <c r="T101" s="3">
         <v>-2000</v>
       </c>
       <c r="U101" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="V101" s="3">
         <v>-1000</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
         <v>-1000</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y101" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-75000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>131000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>26000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-103000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-425000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>277000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-106000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>227000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-202000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>12000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-169000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>264000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-109000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>189000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-85000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-71000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>35000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-429000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-43000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>120000</v>
       </c>
-      <c r="Y102" s="3" t="s">
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
